--- a/assets/平盘银行对账单.xlsx
+++ b/assets/平盘银行对账单.xlsx
@@ -491,7 +491,7 @@
     <col min="12" max="12" width="15.71875" customWidth="1"/>
     <col min="13" max="14" width="20.71875" customWidth="1"/>
     <col min="15" max="16" width="20.71875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20.71875" customWidth="1"/>
+    <col min="17" max="17" width="20.71875" style="1" customWidth="1"/>
     <col min="18" max="18" width="15.71875" customWidth="1"/>
     <col min="19" max="19" width="20.71875" customWidth="1"/>
     <col min="20" max="20" width="20.71875" style="1" customWidth="1"/>
@@ -564,7 +564,7 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="R1" t="s">

--- a/assets/平盘银行对账单.xlsx
+++ b/assets/平盘银行对账单.xlsx
@@ -490,9 +490,8 @@
     <col min="11" max="11" width="15.71875" style="1" customWidth="1"/>
     <col min="12" max="12" width="15.71875" customWidth="1"/>
     <col min="13" max="14" width="20.71875" customWidth="1"/>
-    <col min="15" max="16" width="20.71875" style="1" customWidth="1"/>
-    <col min="17" max="17" width="20.71875" style="1" customWidth="1"/>
-    <col min="18" max="18" width="15.71875" customWidth="1"/>
+    <col min="15" max="17" width="20.71875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="15.71875" style="1" customWidth="1"/>
     <col min="19" max="19" width="20.71875" customWidth="1"/>
     <col min="20" max="20" width="20.71875" style="1" customWidth="1"/>
     <col min="21" max="23" width="20.71875" customWidth="1"/>
@@ -567,7 +566,7 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="S1" t="s">
